--- a/dados/excel/unidade_top20.xlsx
+++ b/dados/excel/unidade_top20.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Dados" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dados'!$A$1:$E$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dados'!$A$1:$F$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -509,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -592,7 +592,7 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -603,7 +603,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>vírgula</t>
+          <t>ponto e vírgula</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026 19:18</t>
+          <t>10/10/2026 14:55</t>
         </is>
       </c>
     </row>
@@ -658,7 +658,7 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>local_trabalho</t>
+          <t>﻿unidade_canonica</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
@@ -675,7 +675,7 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>tipo</t>
+          <t>tipo_unidade</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
@@ -726,15 +726,32 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
+          <t>folha_media</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>moeda</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>Moeda (R$ #,##0,00)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
           <t>ticket_medio</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>moeda</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>Moeda (R$ #,##0,00)</t>
         </is>
@@ -755,25 +772,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="39" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>local_trabalho</t>
+          <t>﻿unidade_canonica</t>
         </is>
       </c>
       <c r="B1" s="5" t="inlineStr">
         <is>
-          <t>tipo</t>
+          <t>tipo_unidade</t>
         </is>
       </c>
       <c r="C1" s="5" t="inlineStr">
@@ -787,6 +805,11 @@
         </is>
       </c>
       <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>folha_media</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>ticket_medio</t>
         </is>
@@ -795,175 +818,199 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>Sedu - Cei 89 (zilda P Aguil)</t>
+          <t>Prof. Eventuais</t>
         </is>
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>Escola</t>
+          <t>Categoria</t>
         </is>
       </c>
       <c r="C2" s="9" t="n">
-        <v>78</v>
+        <v>2746</v>
       </c>
       <c r="D2" s="10" t="n">
-        <v>60547790</v>
+        <v>5784035.99</v>
       </c>
       <c r="E2" s="10" t="n">
-        <v>776253.72</v>
+        <v>2106.349595775674</v>
+      </c>
+      <c r="F2" s="10" t="n">
+        <v>2106.349595775674</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>Sedu - Cei 78 (ettore Marang)</t>
+          <t>GCM — Guarda Civil Municipal</t>
         </is>
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>Escola</t>
+          <t>Setor</t>
         </is>
       </c>
       <c r="C3" s="12" t="n">
-        <v>68</v>
+        <v>514</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>45117425</v>
+        <v>5281522.29</v>
       </c>
       <c r="E3" s="13" t="n">
-        <v>663491.54</v>
+        <v>10275.33519455253</v>
+      </c>
+      <c r="F3" s="13" t="n">
+        <v>10275.33519455253</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>Sedu - em Ary de o Seabra</t>
+          <t>Estágios — Formação Cidadã</t>
         </is>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Escola</t>
+          <t>Categoria</t>
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>64</v>
+        <v>253</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>65862870</v>
+        <v>257016.08</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>1029107.34</v>
+        <v>1015.873833992095</v>
+      </c>
+      <c r="F4" s="10" t="n">
+        <v>1015.873833992095</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>Sedu - em Renice Seraphim</t>
+          <t>Gabinete</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Escola</t>
+          <t>Setor</t>
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>64</v>
+        <v>238</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>55472859</v>
+        <v>4124757.37</v>
       </c>
       <c r="E5" s="13" t="n">
-        <v>866763.42</v>
+        <v>17330.91331932773</v>
+      </c>
+      <c r="F5" s="13" t="n">
+        <v>17330.91331932773</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Sedu - Cei 90 (helio D C Jr)</t>
+          <t>Zoonoses (CCZ)</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Escola</t>
+          <t>Setor</t>
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>62</v>
+        <v>175</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>35186433</v>
+        <v>1290539.33</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>567523.11</v>
+        <v>7374.510457142857</v>
+      </c>
+      <c r="F6" s="10" t="n">
+        <v>7374.510457142857</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>Sedu - Cei 109 (benedicto Pagl</t>
+          <t>Aposentados e Pensionistas (AAPMS)</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Escola</t>
+          <t>Categoria</t>
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>59</v>
+        <v>151</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>40699590</v>
+        <v>952499.63</v>
       </c>
       <c r="E7" s="13" t="n">
-        <v>689823.5600000001</v>
+        <v>6307.944569536424</v>
+      </c>
+      <c r="F7" s="13" t="n">
+        <v>6307.944569536424</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Sedu - em Tereza C Gianini</t>
+          <t>Divisão de Proteção Social Básica</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Escola</t>
+          <t>Setor</t>
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>59</v>
+        <v>100</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>60981490</v>
+        <v>834015.22</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>1033584.58</v>
+        <v>8340.1522</v>
+      </c>
+      <c r="F8" s="10" t="n">
+        <v>8340.1522</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>Sedu - em Ines R Cesarotti</t>
+          <t>Policlínica — Médicos</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Escola</t>
+          <t>Setor</t>
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>55283628</v>
+        <v>1549850.05</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>953166</v>
+        <v>18900.61036585366</v>
+      </c>
+      <c r="F9" s="13" t="n">
+        <v>18900.61036585366</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Sedu - em Achilles Almeida</t>
+          <t>CEI 89 — Zilda P. Aguil</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
@@ -972,40 +1019,46 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>66929460</v>
+        <v>628316.62</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>1174201.05</v>
+        <v>8267.323947368421</v>
+      </c>
+      <c r="F10" s="10" t="n">
+        <v>8267.323947368421</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>Sedu - Cei 107 (arminda da Con</t>
+          <t>SAMU — Enfermagem</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Escola</t>
+          <t>Setor</t>
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>31720210</v>
+        <v>833620</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>556494.91</v>
+        <v>11265.13513513513</v>
+      </c>
+      <c r="F11" s="13" t="n">
+        <v>11265.13513513513</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>Sedu - em Norma Justa D Ara</t>
+          <t>EM Renice Seraphim</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
@@ -1014,19 +1067,22 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>55524877</v>
+        <v>615881.55</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>974120.65</v>
+        <v>9192.261940298507</v>
+      </c>
+      <c r="F12" s="10" t="n">
+        <v>9192.261940298507</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>Sedu - Cei 72 (sueli Gaz Camp)</t>
+          <t>CEI 78 — Ettore Marang</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
@@ -1035,82 +1091,94 @@
         </is>
       </c>
       <c r="C13" s="12" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="D13" s="13" t="n">
-        <v>32591975</v>
+        <v>463864.96</v>
       </c>
       <c r="E13" s="13" t="n">
-        <v>571789.04</v>
+        <v>7028.25696969697</v>
+      </c>
+      <c r="F13" s="13" t="n">
+        <v>7028.25696969697</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>Ses - Ubs Wanel Ville</t>
+          <t>Divisão de Proteção Social Especial</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>UBS</t>
+          <t>Setor</t>
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>50621634</v>
+        <v>537994.33</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>903957.75</v>
+        <v>8406.161406249999</v>
+      </c>
+      <c r="F14" s="10" t="n">
+        <v>8406.161406249999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>Ses - Ubs Aparecidinha</t>
+          <t>EM Ary de O Seabra</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>UBS</t>
+          <t>Escola</t>
         </is>
       </c>
       <c r="C15" s="12" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="D15" s="13" t="n">
-        <v>43590165</v>
+        <v>685382.74</v>
       </c>
       <c r="E15" s="13" t="n">
-        <v>778395.8</v>
+        <v>10879.09111111111</v>
+      </c>
+      <c r="F15" s="13" t="n">
+        <v>10879.09111111111</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>Sedu - Cei 82 (bened M Didi)</t>
+          <t>Transporte de Pacientes — Motoristas</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Escola</t>
+          <t>Setor</t>
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>34871458</v>
+        <v>398525.97</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>622704.61</v>
+        <v>6533.212622950819</v>
+      </c>
+      <c r="F16" s="10" t="n">
+        <v>6533.212622950819</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>Sedu - Cei 73 (matilde Gavin)</t>
+          <t>CEI 90 — Helio D. C. Jr.</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
@@ -1119,61 +1187,70 @@
         </is>
       </c>
       <c r="C17" s="12" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="D17" s="13" t="n">
-        <v>31335471</v>
+        <v>444511.48</v>
       </c>
       <c r="E17" s="13" t="n">
-        <v>569735.84</v>
+        <v>7287.07344262295</v>
+      </c>
+      <c r="F17" s="13" t="n">
+        <v>7287.07344262295</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>Ses - Ubs Ulysses Guimaraes</t>
+          <t>EM Ines R. Cesarotti</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>UBS</t>
+          <t>Escola</t>
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>39203591</v>
+        <v>623472</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>712792.5600000001</v>
+        <v>10391.2</v>
+      </c>
+      <c r="F18" s="10" t="n">
+        <v>10391.2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>Ses - Ubs Rodrigo</t>
+          <t>CEI 109 — Benedicto Pagl</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>UBS</t>
+          <t>Escola</t>
         </is>
       </c>
       <c r="C19" s="12" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="D19" s="13" t="n">
-        <v>47990805</v>
+        <v>429708.28</v>
       </c>
       <c r="E19" s="13" t="n">
-        <v>888718.61</v>
+        <v>7161.804666666666</v>
+      </c>
+      <c r="F19" s="13" t="n">
+        <v>7161.804666666666</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>Sedu - Cei 94 (ana L Pazini)</t>
+          <t>EM Tereza C. Gianini</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -1182,38 +1259,44 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>29322356</v>
+        <v>660700.65</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>543006.59</v>
+        <v>11198.31610169492</v>
+      </c>
+      <c r="F20" s="10" t="n">
+        <v>11198.31610169492</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>Ses - Ubs Marcia Mendes</t>
+          <t>EM Achilles Almeida</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>UBS</t>
+          <t>Escola</t>
         </is>
       </c>
       <c r="C21" s="12" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D21" s="13" t="n">
-        <v>47902667</v>
+        <v>680971.87</v>
       </c>
       <c r="E21" s="13" t="n">
-        <v>903823.91</v>
+        <v>11946.8749122807</v>
+      </c>
+      <c r="F21" s="13" t="n">
+        <v>11946.8749122807</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E21"/>
+  <autoFilter ref="A1:F21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>